--- a/output/estat-desc.xlsx
+++ b/output/estat-desc.xlsx
@@ -1099,43 +1099,43 @@
         </is>
       </c>
       <c r="D14">
-        <v>2.175125067527062E-05</v>
+        <v>2.175125067527062e-05</v>
       </c>
       <c r="E14">
         <v>0.0001023867517258437</v>
       </c>
       <c r="F14">
-        <v>2.94574717118082E-127</v>
+        <v>2.94574717118082e-127</v>
       </c>
       <c r="G14">
-        <v>2.018899192295169E-06</v>
+        <v>2.018899192295169e-06</v>
       </c>
       <c r="H14">
-        <v>1.231819906436174E-05</v>
+        <v>1.231819906436174e-05</v>
       </c>
       <c r="I14">
-        <v>2.172230516570348E-28</v>
+        <v>2.172230516570348e-28</v>
       </c>
       <c r="J14">
-        <v>3.018942741614563E-07</v>
+        <v>3.018942741614563e-07</v>
       </c>
       <c r="K14">
-        <v>3.559064184832121E-05</v>
+        <v>3.559064184832121e-05</v>
       </c>
       <c r="L14">
-        <v>2.288283733418591E-13</v>
+        <v>2.288283733418591e-13</v>
       </c>
       <c r="M14">
-        <v>1.486026805631738E-05</v>
+        <v>1.486026805631738e-05</v>
       </c>
       <c r="N14">
-        <v>5.17428850667079E-05</v>
+        <v>5.17428850667079e-05</v>
       </c>
       <c r="O14">
         <v>0.1348066270549246</v>
       </c>
       <c r="P14">
-        <v>8.110736823623348E-21</v>
+        <v>8.110736823623348e-21</v>
       </c>
     </row>
     <row r="15">
@@ -1153,13 +1153,13 @@
         </is>
       </c>
       <c r="D15">
-        <v>2.733432181074702E-06</v>
+        <v>2.733432181074702e-06</v>
       </c>
       <c r="E15">
         <v>0.01153315223895822</v>
       </c>
       <c r="F15">
-        <v>4.039473340474221E-19</v>
+        <v>4.039473340474221e-19</v>
       </c>
       <c r="G15">
         <v>0.0002530115150777753</v>
@@ -1174,7 +1174,7 @@
         <v>0.03817720542502946</v>
       </c>
       <c r="K15">
-        <v>1.129984840553548E-16</v>
+        <v>1.129984840553548e-16</v>
       </c>
       <c r="L15">
         <v>0.1868499680246174</v>
@@ -1858,40 +1858,40 @@
         <v>0.0001253951527867442</v>
       </c>
       <c r="E28">
-        <v>7.325178185298197E-05</v>
+        <v>7.325178185298197e-05</v>
       </c>
       <c r="F28">
-        <v>1.624177290660182E-79</v>
+        <v>1.624177290660182e-79</v>
       </c>
       <c r="G28">
-        <v>1.144061277295893E-05</v>
+        <v>1.144061277295893e-05</v>
       </c>
       <c r="H28">
-        <v>4.366501938523301E-08</v>
+        <v>4.366501938523301e-08</v>
       </c>
       <c r="I28">
-        <v>9.672474556185454E-18</v>
+        <v>9.672474556185454e-18</v>
       </c>
       <c r="J28">
-        <v>1.689997590731012E-28</v>
+        <v>1.689997590731012e-28</v>
       </c>
       <c r="K28">
-        <v>8.511564386591767E-08</v>
+        <v>8.511564386591767e-08</v>
       </c>
       <c r="L28">
-        <v>2.497448913470172E-43</v>
+        <v>2.497448913470172e-43</v>
       </c>
       <c r="M28">
-        <v>6.97459049794049E-10</v>
+        <v>6.97459049794049e-10</v>
       </c>
       <c r="N28">
-        <v>4.302563619621062E-05</v>
+        <v>4.302563619621062e-05</v>
       </c>
       <c r="O28">
         <v>0.01102358784240185</v>
       </c>
       <c r="P28">
-        <v>5.172408963102356E-28</v>
+        <v>5.172408963102356e-28</v>
       </c>
     </row>
     <row r="29">
@@ -1912,13 +1912,13 @@
         <v>0.0009061561632760605</v>
       </c>
       <c r="E29">
-        <v>1.154062828826441E-06</v>
+        <v>1.154062828826441e-06</v>
       </c>
       <c r="F29">
-        <v>2.285723697183008E-07</v>
+        <v>2.285723697183008e-07</v>
       </c>
       <c r="G29">
-        <v>4.06479534660379E-08</v>
+        <v>4.06479534660379e-08</v>
       </c>
       <c r="H29">
         <v>0.0705697349272732</v>
@@ -1930,10 +1930,10 @@
         <v>0.0002327621394622558</v>
       </c>
       <c r="K29">
-        <v>1.493923427225125E-23</v>
+        <v>1.493923427225125e-23</v>
       </c>
       <c r="L29">
-        <v>2.529885739335968E-06</v>
+        <v>2.529885739335968e-06</v>
       </c>
       <c r="M29">
         <v>0.002214285324131057</v>
@@ -2611,34 +2611,34 @@
         </is>
       </c>
       <c r="D42">
-        <v>3.556377916917322E-05</v>
+        <v>3.556377916917322e-05</v>
       </c>
       <c r="E42">
-        <v>6.308277101313254E-12</v>
+        <v>6.308277101313254e-12</v>
       </c>
       <c r="F42">
-        <v>6.788758437654391E-120</v>
+        <v>6.788758437654391e-120</v>
       </c>
       <c r="G42">
-        <v>8.444312380605065E-11</v>
+        <v>8.444312380605065e-11</v>
       </c>
       <c r="H42">
-        <v>1.079859156867694E-12</v>
+        <v>1.079859156867694e-12</v>
       </c>
       <c r="I42">
-        <v>1.058330620461284E-35</v>
+        <v>1.058330620461284e-35</v>
       </c>
       <c r="J42">
-        <v>1.350050723231868E-12</v>
+        <v>1.350050723231868e-12</v>
       </c>
       <c r="K42">
-        <v>2.153670477125398E-06</v>
+        <v>2.153670477125398e-06</v>
       </c>
       <c r="L42">
-        <v>5.621224238275127E-28</v>
+        <v>5.621224238275127e-28</v>
       </c>
       <c r="M42">
-        <v>2.716488168954023E-11</v>
+        <v>2.716488168954023e-11</v>
       </c>
       <c r="N42">
         <v>0.003543123848253125</v>
@@ -2647,7 +2647,7 @@
         <v>0.08864031151392954</v>
       </c>
       <c r="P42">
-        <v>5.354602293376872E-32</v>
+        <v>5.354602293376872e-32</v>
       </c>
     </row>
     <row r="43">
@@ -2665,13 +2665,13 @@
         </is>
       </c>
       <c r="D43">
-        <v>8.061493344226834E-06</v>
+        <v>8.061493344226834e-06</v>
       </c>
       <c r="E43">
         <v>0.1669913157547267</v>
       </c>
       <c r="F43">
-        <v>5.733834926561614E-29</v>
+        <v>5.733834926561614e-29</v>
       </c>
       <c r="G43">
         <v>0.2760146083672259</v>
@@ -2686,7 +2686,7 @@
         <v>0.2574315986593589</v>
       </c>
       <c r="K43">
-        <v>6.648422029889754E-17</v>
+        <v>6.648422029889754e-17</v>
       </c>
       <c r="L43">
         <v>0.0001536630967093455</v>
@@ -3367,43 +3367,43 @@
         </is>
       </c>
       <c r="D56">
-        <v>4.345152154703439E-14</v>
+        <v>4.345152154703439e-14</v>
       </c>
       <c r="E56">
-        <v>1.176515060131585E-11</v>
+        <v>1.176515060131585e-11</v>
       </c>
       <c r="F56">
-        <v>9.306478706001928E-81</v>
+        <v>9.306478706001928e-81</v>
       </c>
       <c r="G56">
-        <v>1.386248525153298E-12</v>
+        <v>1.386248525153298e-12</v>
       </c>
       <c r="H56">
-        <v>3.295434523276407E-07</v>
+        <v>3.295434523276407e-07</v>
       </c>
       <c r="I56">
-        <v>2.043877171779886E-70</v>
+        <v>2.043877171779886e-70</v>
       </c>
       <c r="J56">
-        <v>5.800742412002618E-10</v>
+        <v>5.800742412002618e-10</v>
       </c>
       <c r="K56">
         <v>0.0003338264244968588</v>
       </c>
       <c r="L56">
-        <v>3.297207040110283E-42</v>
+        <v>3.297207040110283e-42</v>
       </c>
       <c r="M56">
-        <v>1.889130040854983E-10</v>
+        <v>1.889130040854983e-10</v>
       </c>
       <c r="N56">
-        <v>1.219853834865889E-13</v>
+        <v>1.219853834865889e-13</v>
       </c>
       <c r="O56">
         <v>0.00322379835582983</v>
       </c>
       <c r="P56">
-        <v>2.25213746729111E-29</v>
+        <v>2.25213746729111e-29</v>
       </c>
     </row>
     <row r="57">
@@ -3421,13 +3421,13 @@
         </is>
       </c>
       <c r="D57">
-        <v>9.182797812667183E-05</v>
+        <v>9.182797812667183e-05</v>
       </c>
       <c r="E57">
         <v>0.7673462113564113</v>
       </c>
       <c r="F57">
-        <v>6.826593736435667E-12</v>
+        <v>6.826593736435667e-12</v>
       </c>
       <c r="G57">
         <v>0.2928081843054446</v>
@@ -3436,16 +3436,16 @@
         <v>0.5270617283351768</v>
       </c>
       <c r="I57">
-        <v>1.893885510023975E-06</v>
+        <v>1.893885510023975e-06</v>
       </c>
       <c r="J57">
         <v>0.1185516822253643</v>
       </c>
       <c r="K57">
-        <v>8.036034299088005E-13</v>
+        <v>8.036034299088005e-13</v>
       </c>
       <c r="L57">
-        <v>5.772897933040733E-10</v>
+        <v>5.772897933040733e-10</v>
       </c>
       <c r="M57">
         <v>0.002502294868730493</v>
@@ -4123,43 +4123,43 @@
         </is>
       </c>
       <c r="D70">
-        <v>2.61500531317753E-20</v>
+        <v>2.61500531317753e-20</v>
       </c>
       <c r="E70">
-        <v>3.112736239854305E-09</v>
+        <v>3.112736239854305e-09</v>
       </c>
       <c r="F70">
-        <v>5.339490572524831E-120</v>
+        <v>5.339490572524831e-120</v>
       </c>
       <c r="G70">
-        <v>2.207419456544884E-05</v>
+        <v>2.207419456544884e-05</v>
       </c>
       <c r="H70">
-        <v>9.087301934861568E-11</v>
+        <v>9.087301934861568e-11</v>
       </c>
       <c r="I70">
-        <v>2.516604461890122E-60</v>
+        <v>2.516604461890122e-60</v>
       </c>
       <c r="J70">
-        <v>2.056893808266116E-23</v>
+        <v>2.056893808266116e-23</v>
       </c>
       <c r="K70">
         <v>0.004627127605562165</v>
       </c>
       <c r="L70">
-        <v>8.38868855274642E-24</v>
+        <v>8.38868855274642e-24</v>
       </c>
       <c r="M70">
-        <v>1.435413702086297E-05</v>
+        <v>1.435413702086297e-05</v>
       </c>
       <c r="N70">
-        <v>5.875976632936747E-07</v>
+        <v>5.875976632936747e-07</v>
       </c>
       <c r="O70">
         <v>0.03173032596331914</v>
       </c>
       <c r="P70">
-        <v>4.883410895401522E-42</v>
+        <v>4.883410895401522e-42</v>
       </c>
     </row>
     <row r="71">
@@ -4177,13 +4177,13 @@
         </is>
       </c>
       <c r="D71">
-        <v>1.548236222062788E-08</v>
+        <v>1.548236222062788e-08</v>
       </c>
       <c r="E71">
         <v>0.9959148069862214</v>
       </c>
       <c r="F71">
-        <v>4.996067556992662E-39</v>
+        <v>4.996067556992662e-39</v>
       </c>
       <c r="G71">
         <v>0.2514712990391743</v>
@@ -4192,16 +4192,16 @@
         <v>0.04839861941987011</v>
       </c>
       <c r="I71">
-        <v>5.104024518804958E-09</v>
+        <v>5.104024518804958e-09</v>
       </c>
       <c r="J71">
         <v>0.0942305162024754</v>
       </c>
       <c r="K71">
-        <v>2.59381012630379E-09</v>
+        <v>2.59381012630379e-09</v>
       </c>
       <c r="L71">
-        <v>1.61772758302341E-07</v>
+        <v>1.61772758302341e-07</v>
       </c>
       <c r="M71">
         <v>0.2453030075332645</v>
@@ -4213,7 +4213,7 @@
         <v>0.03210027565950649</v>
       </c>
       <c r="P71">
-        <v>4.042864854710428E-07</v>
+        <v>4.042864854710428e-07</v>
       </c>
     </row>
     <row r="72">
@@ -4879,43 +4879,43 @@
         </is>
       </c>
       <c r="D84">
-        <v>5.499225525056871E-18</v>
+        <v>5.499225525056871e-18</v>
       </c>
       <c r="E84">
-        <v>6.066123811564746E-12</v>
+        <v>6.066123811564746e-12</v>
       </c>
       <c r="F84">
-        <v>9.259018813329305E-96</v>
+        <v>9.259018813329305e-96</v>
       </c>
       <c r="G84">
-        <v>8.125262568346537E-14</v>
+        <v>8.125262568346537e-14</v>
       </c>
       <c r="H84">
-        <v>3.237152433376887E-21</v>
+        <v>3.237152433376887e-21</v>
       </c>
       <c r="I84">
-        <v>4.287337639094643E-37</v>
+        <v>4.287337639094643e-37</v>
       </c>
       <c r="J84">
-        <v>8.393163806367333E-17</v>
+        <v>8.393163806367333e-17</v>
       </c>
       <c r="K84">
         <v>0.0007632042179251747</v>
       </c>
       <c r="L84">
-        <v>4.899234550066798E-46</v>
+        <v>4.899234550066798e-46</v>
       </c>
       <c r="M84">
-        <v>5.738063385144393E-08</v>
+        <v>5.738063385144393e-08</v>
       </c>
       <c r="N84">
-        <v>3.280053821858778E-14</v>
+        <v>3.280053821858778e-14</v>
       </c>
       <c r="O84">
         <v>0.04484533000821043</v>
       </c>
       <c r="P84">
-        <v>6.382494946561446E-40</v>
+        <v>6.382494946561446e-40</v>
       </c>
     </row>
     <row r="85">
@@ -4933,13 +4933,13 @@
         </is>
       </c>
       <c r="D85">
-        <v>6.974537488931162E-14</v>
+        <v>6.974537488931162e-14</v>
       </c>
       <c r="E85">
         <v>0.7168834543202092</v>
       </c>
       <c r="F85">
-        <v>2.784189962211044E-20</v>
+        <v>2.784189962211044e-20</v>
       </c>
       <c r="G85">
         <v>0.1402247141152468</v>
@@ -4948,16 +4948,16 @@
         <v>0.0001031252393508702</v>
       </c>
       <c r="I85">
-        <v>1.315037262157936E-07</v>
+        <v>1.315037262157936e-07</v>
       </c>
       <c r="J85">
         <v>0.0004636697352625229</v>
       </c>
       <c r="K85">
-        <v>1.348360519719634E-12</v>
+        <v>1.348360519719634e-12</v>
       </c>
       <c r="L85">
-        <v>2.51787369963396E-15</v>
+        <v>2.51787369963396e-15</v>
       </c>
       <c r="M85">
         <v>0.01517580591826713</v>
@@ -4969,7 +4969,7 @@
         <v>0.08695487214687116</v>
       </c>
       <c r="P85">
-        <v>8.245919328489589E-07</v>
+        <v>8.245919328489589e-07</v>
       </c>
     </row>
   </sheetData>
